--- a/src/data/images_tombstones.xlsx
+++ b/src/data/images_tombstones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_projects\tombstones\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321C6D5A-F49B-4B40-927E-17C778AE714F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C722B57-4F52-4A82-A6D3-25FBD3DDEECB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -799,9 +799,6 @@
     <t>Nizhnie_Meteski_2_id13.jpg</t>
   </si>
   <si>
-    <t>Nizhnyaya_Ura 1_id4.jpg</t>
-  </si>
-  <si>
     <t>Nizhnyaya_Ura_2_id5.jpg</t>
   </si>
   <si>
@@ -1007,6 +1004,9 @@
   </si>
   <si>
     <t>Nalasa_Kladbishe_2_id46.jpg</t>
+  </si>
+  <si>
+    <t>Nizhnyaya_Ura_1_id4.jpg</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2015,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
@@ -2034,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
@@ -2053,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
@@ -2072,7 +2072,7 @@
         <v>58</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4">
@@ -2091,7 +2091,7 @@
         <v>52</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4">
@@ -2110,7 +2110,7 @@
         <v>53</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
@@ -2129,7 +2129,7 @@
         <v>74</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
@@ -2148,7 +2148,7 @@
         <v>75</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
@@ -2167,7 +2167,7 @@
         <v>21</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
@@ -2186,7 +2186,7 @@
         <v>20</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4">
@@ -2205,7 +2205,7 @@
         <v>17</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
@@ -2224,7 +2224,7 @@
         <v>18</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
@@ -2243,7 +2243,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
@@ -2262,7 +2262,7 @@
         <v>23</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
@@ -2281,7 +2281,7 @@
         <v>24</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
@@ -2300,7 +2300,7 @@
         <v>25</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4">
@@ -2319,7 +2319,7 @@
         <v>42</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
@@ -2338,7 +2338,7 @@
         <v>43</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4">
@@ -2357,7 +2357,7 @@
         <v>7</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4">
@@ -2376,7 +2376,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
@@ -2395,7 +2395,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4">
@@ -2414,7 +2414,7 @@
         <v>63</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4">
@@ -2433,7 +2433,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
@@ -2452,7 +2452,7 @@
         <v>57</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4">
@@ -2471,7 +2471,7 @@
         <v>62</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4">
@@ -2490,7 +2490,7 @@
         <v>61</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4">
@@ -2509,7 +2509,7 @@
         <v>60</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4">
@@ -2528,7 +2528,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4">
@@ -2547,7 +2547,7 @@
         <v>12</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4">
@@ -2566,7 +2566,7 @@
         <v>73</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4">
@@ -2585,7 +2585,7 @@
         <v>54</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4">
@@ -2604,7 +2604,7 @@
         <v>55</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4">
@@ -2623,7 +2623,7 @@
         <v>71</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4">
@@ -2642,7 +2642,7 @@
         <v>68</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4">
@@ -2661,7 +2661,7 @@
         <v>69</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4">
@@ -2680,7 +2680,7 @@
         <v>67</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4">
@@ -2699,7 +2699,7 @@
         <v>59</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4">
@@ -2718,7 +2718,7 @@
         <v>19</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4">
@@ -2737,7 +2737,7 @@
         <v>64</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4">
@@ -2756,7 +2756,7 @@
         <v>65</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4">
@@ -2775,7 +2775,7 @@
         <v>28</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4">
@@ -2794,7 +2794,7 @@
         <v>30</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4">
@@ -2813,7 +2813,7 @@
         <v>31</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4">
@@ -2832,7 +2832,7 @@
         <v>33</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4">
@@ -2851,7 +2851,7 @@
         <v>32</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4">
@@ -2870,7 +2870,7 @@
         <v>29</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4">
@@ -2889,7 +2889,7 @@
         <v>40</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4">
@@ -2908,7 +2908,7 @@
         <v>49</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4">
@@ -2927,7 +2927,7 @@
         <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4">
@@ -2946,7 +2946,7 @@
         <v>72</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4">
@@ -2965,7 +2965,7 @@
         <v>66</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4">
@@ -2984,7 +2984,7 @@
         <v>70</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4">
@@ -3003,7 +3003,7 @@
         <v>48</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4">
@@ -3022,7 +3022,7 @@
         <v>36</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4">
@@ -3041,7 +3041,7 @@
         <v>38</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4">
@@ -3060,7 +3060,7 @@
         <v>37</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4">
@@ -3079,7 +3079,7 @@
         <v>39</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4">
@@ -3098,7 +3098,7 @@
         <v>50</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4">
@@ -3117,7 +3117,7 @@
         <v>51</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4">
@@ -3136,7 +3136,7 @@
         <v>10</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4">
@@ -3155,7 +3155,7 @@
         <v>41</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4">
@@ -3174,7 +3174,7 @@
         <v>26</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4">
@@ -3193,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="4">
@@ -3212,7 +3212,7 @@
         <v>34</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4">
@@ -3231,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4">
@@ -3250,7 +3250,7 @@
         <v>35</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4">
@@ -3269,7 +3269,7 @@
         <v>35</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4">
@@ -3288,7 +3288,7 @@
         <v>44</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4">
@@ -3307,7 +3307,7 @@
         <v>45</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4">
@@ -3326,7 +3326,7 @@
         <v>46</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4">

--- a/src/data/images_tombstones.xlsx
+++ b/src/data/images_tombstones.xlsx
@@ -8,14 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_projects\tombstones\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C722B57-4F52-4A82-A6D3-25FBD3DDEECB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DC4710-59D9-443C-BBCC-BDC0E3D270D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="images_Faces" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -184,48 +192,6 @@
     <t>2023_05_03_Srednyaya_Kladbishe_Serda_front_ortho_3.jpg</t>
   </si>
   <si>
-    <t>2023_05_03_Srednyaya_Serda_1_back_dem_id22.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_1_back_ortho_id22.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_1_front_dem_id22.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_1_front_ortho_id22.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_2_back_dem_id23.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_2_back_ortho_id23.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_2_front_dem_id23.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_2_front_ortho_id23.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_back_dem.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_back_ortho.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_front_dem.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_front_ortho.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_Kladbishe_2_front_dem_id25.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Serda_Kladbishe_2_front_ortho_id25.jpg</t>
-  </si>
-  <si>
     <t>2023_05_03_Srednyaya_Serda_Kladbishe_3_left_dem_id24.jpg</t>
   </si>
   <si>
@@ -1007,6 +973,48 @@
   </si>
   <si>
     <t>Nizhnyaya_Ura_1_id4.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_1_back_dem_id17.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_1_back_ortho_id17.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_1_front_dem_id17.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_1_front_ortho_id17.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_2_back_dem_id18.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_2_back_ortho_id18.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_2_front_dem_id18.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_2_front_ortho_id18.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_Kladbishe_2_front_dem_id23.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_Kladbishe_2_front_ortho_id23.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_back_dem_id22.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_back_ortho_id22.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_front_dem_id22.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_front_ortho_id22.jpg</t>
   </si>
 </sst>
 </file>
@@ -1917,7 +1925,7 @@
     <col min="2" max="2" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
@@ -1925,40 +1933,40 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D2" s="4">
         <v>47</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
@@ -1967,17 +1975,17 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D3" s="4">
         <v>14</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
@@ -1986,17 +1994,17 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D4" s="4">
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
@@ -2005,17 +2013,17 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D5" s="4">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
@@ -2024,17 +2032,17 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D6" s="4">
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
@@ -2043,17 +2051,17 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D7" s="4">
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
@@ -2062,17 +2070,17 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D8" s="4">
         <v>58</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4">
@@ -2081,17 +2089,17 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D9" s="4">
         <v>52</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4">
@@ -2100,17 +2108,17 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D10" s="4">
         <v>53</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
@@ -2119,17 +2127,17 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D11" s="4">
         <v>74</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
@@ -2138,17 +2146,17 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D12" s="4">
         <v>75</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
@@ -2157,17 +2165,17 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D13" s="4">
         <v>21</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
@@ -2176,17 +2184,17 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D14" s="4">
         <v>20</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4">
@@ -2195,17 +2203,17 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D15" s="4">
         <v>17</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
@@ -2214,17 +2222,17 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D16" s="4">
         <v>18</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
@@ -2233,17 +2241,17 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D17" s="4">
         <v>22</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
@@ -2252,17 +2260,17 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D18" s="4">
         <v>23</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
@@ -2271,17 +2279,17 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D19" s="4">
         <v>24</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
@@ -2290,17 +2298,17 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D20" s="4">
         <v>25</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4">
@@ -2309,17 +2317,17 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D21" s="4">
         <v>42</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
@@ -2328,17 +2336,17 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D22" s="4">
         <v>43</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4">
@@ -2347,17 +2355,17 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D23" s="4">
         <v>7</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4">
@@ -2366,17 +2374,17 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D24" s="4">
         <v>8</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
@@ -2385,17 +2393,17 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D25" s="4">
         <v>9</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4">
@@ -2404,17 +2412,17 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D26" s="4">
         <v>63</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4">
@@ -2423,17 +2431,17 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
@@ -2442,17 +2450,17 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D28" s="4">
         <v>57</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4">
@@ -2461,17 +2469,17 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D29" s="4">
         <v>62</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4">
@@ -2480,17 +2488,17 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D30" s="4">
         <v>61</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4">
@@ -2499,17 +2507,17 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D31" s="4">
         <v>60</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4">
@@ -2518,17 +2526,17 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D32" s="4">
         <v>11</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4">
@@ -2537,17 +2545,17 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D33" s="4">
         <v>12</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4">
@@ -2556,17 +2564,17 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D34" s="4">
         <v>73</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4">
@@ -2575,17 +2583,17 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D35" s="4">
         <v>54</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4">
@@ -2594,17 +2602,17 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D36" s="4">
         <v>55</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4">
@@ -2613,17 +2621,17 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D37" s="4">
         <v>71</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4">
@@ -2632,17 +2640,17 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D38" s="4">
         <v>68</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4">
@@ -2651,17 +2659,17 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D39" s="4">
         <v>69</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4">
@@ -2670,17 +2678,17 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D40" s="4">
         <v>67</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4">
@@ -2689,17 +2697,17 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D41" s="4">
         <v>59</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4">
@@ -2708,17 +2716,17 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D42" s="4">
         <v>19</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4">
@@ -2727,17 +2735,17 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D43" s="4">
         <v>64</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4">
@@ -2746,17 +2754,17 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D44" s="4">
         <v>65</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4">
@@ -2765,17 +2773,17 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D45" s="4">
         <v>28</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4">
@@ -2784,17 +2792,17 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D46" s="4">
         <v>30</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4">
@@ -2803,17 +2811,17 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D47" s="4">
         <v>31</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4">
@@ -2822,17 +2830,17 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D48" s="4">
         <v>33</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4">
@@ -2841,17 +2849,17 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D49" s="4">
         <v>32</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4">
@@ -2860,17 +2868,17 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D50" s="4">
         <v>29</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4">
@@ -2879,17 +2887,17 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D51" s="4">
         <v>40</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4">
@@ -2898,17 +2906,17 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D52" s="4">
         <v>49</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4">
@@ -2917,17 +2925,17 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D53" s="4">
         <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4">
@@ -2936,17 +2944,17 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D54" s="4">
         <v>72</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4">
@@ -2955,17 +2963,17 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D55" s="4">
         <v>66</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4">
@@ -2974,17 +2982,17 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D56" s="4">
         <v>70</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4">
@@ -2993,17 +3001,17 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D57" s="4">
         <v>48</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4">
@@ -3012,17 +3020,17 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D58" s="4">
         <v>36</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4">
@@ -3031,17 +3039,17 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D59" s="4">
         <v>38</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4">
@@ -3050,17 +3058,17 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D60" s="4">
         <v>37</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4">
@@ -3069,17 +3077,17 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D61" s="4">
         <v>39</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4">
@@ -3088,17 +3096,17 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D62" s="4">
         <v>50</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4">
@@ -3107,17 +3115,17 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D63" s="4">
         <v>51</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4">
@@ -3126,17 +3134,17 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D64" s="4">
         <v>10</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4">
@@ -3145,17 +3153,17 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D65" s="4">
         <v>41</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4">
@@ -3164,17 +3172,17 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D66" s="4">
         <v>26</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4">
@@ -3183,17 +3191,17 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D67" s="4">
         <v>27</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="4">
@@ -3202,17 +3210,17 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D68" s="4">
         <v>34</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4">
@@ -3221,17 +3229,17 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D69" s="4">
         <v>1</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4">
@@ -3240,17 +3248,17 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D70" s="4">
         <v>35</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4">
@@ -3259,36 +3267,36 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D71" s="4">
         <v>35</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D72" s="4">
         <v>44</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4">
@@ -3297,17 +3305,17 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D73" s="4">
         <v>45</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4">
@@ -3316,17 +3324,17 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D74" s="4">
         <v>46</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4">
@@ -3335,13 +3343,13 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -3356,16 +3364,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D76" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>1</v>
@@ -3377,13 +3385,13 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D77" s="3">
         <v>4</v>
@@ -3398,16 +3406,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D78" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>3</v>
@@ -3419,16 +3427,16 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D79" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>4</v>
@@ -3440,16 +3448,16 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D80" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>5</v>
@@ -3461,16 +3469,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D81" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>6</v>
@@ -3482,16 +3490,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D82" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>7</v>
@@ -3503,16 +3511,16 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D83" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
@@ -3524,16 +3532,16 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D84" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>9</v>
@@ -3545,16 +3553,16 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D85" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>10</v>
@@ -3566,16 +3574,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D86" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>11</v>
@@ -3587,16 +3595,16 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D87" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>12</v>
@@ -3608,16 +3616,16 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D88" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>13</v>
@@ -3629,16 +3637,16 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D89" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>14</v>
@@ -3650,16 +3658,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D90" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>15</v>
@@ -3671,16 +3679,16 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D91" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>16</v>
@@ -3692,16 +3700,16 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D92" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>17</v>
@@ -3713,16 +3721,16 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D93" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>18</v>
@@ -3734,16 +3742,16 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D94" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>19</v>
@@ -3755,16 +3763,16 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D95" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>20</v>
@@ -3776,16 +3784,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D96" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>21</v>
@@ -3797,16 +3805,16 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D97" s="3">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>22</v>
@@ -3818,16 +3826,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D98" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>23</v>
@@ -3839,16 +3847,16 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D99" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>24</v>
@@ -3860,16 +3868,16 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D100" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>25</v>
@@ -3881,16 +3889,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D101" s="3">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>26</v>
@@ -3902,16 +3910,16 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D102" s="3">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>27</v>
@@ -3923,16 +3931,16 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D103" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>28</v>
@@ -3944,16 +3952,16 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D104" s="3">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>29</v>
@@ -3965,16 +3973,16 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D105" s="3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>30</v>
@@ -3986,16 +3994,16 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D106" s="3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>31</v>
@@ -4007,16 +4015,16 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D107" s="3">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>32</v>
@@ -4028,16 +4036,16 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D108" s="3">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>33</v>
@@ -4049,16 +4057,16 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D109" s="3">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>34</v>
@@ -4070,16 +4078,16 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D110" s="3">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>35</v>
@@ -4091,16 +4099,16 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D111" s="3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>36</v>
@@ -4112,16 +4120,16 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D112" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>37</v>
@@ -4133,16 +4141,16 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D113" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>38</v>
@@ -4154,16 +4162,16 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D114" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>39</v>
@@ -4175,16 +4183,16 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D115" s="3">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>40</v>
@@ -4196,16 +4204,16 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D116" s="3">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>41</v>
@@ -4217,16 +4225,16 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D117" s="3">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>42</v>
@@ -4238,16 +4246,16 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D118" s="3">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>43</v>
@@ -4259,16 +4267,16 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D119" s="3">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>44</v>
@@ -4280,16 +4288,16 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D120" s="3">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>45</v>
@@ -4301,16 +4309,16 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D121" s="3">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>46</v>
@@ -4322,16 +4330,16 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D122" s="3">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>47</v>
@@ -4343,16 +4351,16 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D123" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>48</v>
@@ -4364,16 +4372,16 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D124" s="3">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>49</v>
@@ -4385,16 +4393,16 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D125" s="3">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>50</v>
@@ -4406,16 +4414,16 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D126" s="3">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>51</v>
@@ -4427,16 +4435,16 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D127" s="3">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>52</v>
@@ -4448,16 +4456,16 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D128" s="3">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>53</v>
@@ -4469,19 +4477,19 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D129" s="3">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>54</v>
+        <v>315</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="3">
@@ -4490,19 +4498,19 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D130" s="3">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>55</v>
+        <v>316</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="3">
@@ -4511,19 +4519,19 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D131" s="3">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>56</v>
+        <v>317</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="3">
@@ -4532,19 +4540,19 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D132" s="3">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>57</v>
+        <v>318</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="3">
@@ -4553,19 +4561,19 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D133" s="3">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>58</v>
+        <v>319</v>
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="3">
@@ -4574,19 +4582,19 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D134" s="3">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>59</v>
+        <v>320</v>
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="3">
@@ -4595,19 +4603,19 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D135" s="3">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>60</v>
+        <v>321</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3">
@@ -4616,19 +4624,19 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D136" s="3">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>61</v>
+        <v>322</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3">
@@ -4637,19 +4645,19 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D137" s="3">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>62</v>
+        <v>325</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3">
@@ -4658,19 +4666,19 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D138" s="3">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="F138" s="3"/>
       <c r="G138" s="3">
@@ -4679,19 +4687,19 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D139" s="3">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>64</v>
+        <v>327</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3">
@@ -4700,19 +4708,19 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D140" s="3">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="3">
@@ -4721,19 +4729,19 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D141" s="3">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>66</v>
+        <v>323</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3">
@@ -4742,19 +4750,19 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D142" s="3">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>67</v>
+        <v>324</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3">
@@ -4763,19 +4771,19 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D143" s="3">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3">
@@ -4784,19 +4792,19 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D144" s="3">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3">
@@ -4805,19 +4813,19 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D145" s="3">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3">
@@ -4826,19 +4834,19 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D146" s="3">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3">
@@ -4847,19 +4855,19 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D147" s="3">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3">
@@ -4868,19 +4876,19 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D148" s="3">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3">
@@ -4889,19 +4897,19 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D149" s="3">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3">
@@ -4910,19 +4918,19 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D150" s="3">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="3">
@@ -4931,19 +4939,19 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D151" s="3">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3">
@@ -4952,19 +4960,19 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D152" s="3">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3">
@@ -4973,19 +4981,19 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D153" s="3">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3">
@@ -4994,19 +5002,19 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D154" s="3">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3">
@@ -5015,19 +5023,19 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D155" s="3">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3">
@@ -5036,19 +5044,19 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D156" s="3">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3">
@@ -5057,19 +5065,19 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D157" s="3">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3">
@@ -5078,19 +5086,19 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D158" s="3">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3">
@@ -5099,19 +5107,19 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D159" s="3">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3">
@@ -5120,19 +5128,19 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D160" s="3">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3">
@@ -5141,19 +5149,19 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D161" s="3">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3">
@@ -5162,19 +5170,19 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D162" s="3">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3">
@@ -5183,19 +5191,19 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D163" s="3">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3">
@@ -5204,19 +5212,19 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D164" s="3">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3">
@@ -5225,19 +5233,19 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D165" s="3">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3">
@@ -5246,19 +5254,19 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D166" s="3">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3">
@@ -5267,19 +5275,19 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D167" s="3">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3">
@@ -5288,19 +5296,19 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D168" s="3">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3">
@@ -5309,19 +5317,19 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D169" s="3">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3">
@@ -5330,19 +5338,19 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D170" s="3">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3">
@@ -5351,19 +5359,19 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D171" s="3">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3">
@@ -5372,19 +5380,19 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D172" s="3">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3">
@@ -5393,19 +5401,19 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D173" s="3">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3">
@@ -5414,19 +5422,19 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D174" s="3">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3">
@@ -5435,19 +5443,19 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D175" s="3">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3">
@@ -5456,19 +5464,19 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D176" s="3">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3">
@@ -5477,19 +5485,19 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D177" s="3">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3">
@@ -5498,19 +5506,19 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D178" s="3">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3">
@@ -5519,19 +5527,19 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D179" s="3">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3">
@@ -5540,19 +5548,19 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D180" s="3">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3">
@@ -5561,19 +5569,19 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D181" s="3">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3">
@@ -5582,19 +5590,19 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D182" s="3">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3">
@@ -5603,19 +5611,19 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D183" s="3">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3">
@@ -5624,19 +5632,19 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D184" s="3">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3">
@@ -5645,19 +5653,19 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D185" s="3">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3">
@@ -5666,19 +5674,19 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D186" s="3">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3">
@@ -5687,19 +5695,19 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D187" s="3">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3">
@@ -5708,19 +5716,19 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D188" s="3">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3">
@@ -5729,19 +5737,19 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D189" s="3">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3">
@@ -5750,19 +5758,19 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D190" s="3">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3">
@@ -5771,19 +5779,19 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D191" s="3">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3">
@@ -5792,19 +5800,19 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D192" s="3">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3">
@@ -5813,19 +5821,19 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D193" s="3">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3">
@@ -5834,19 +5842,19 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D194" s="3">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3">
@@ -5855,19 +5863,19 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D195" s="3">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3">
@@ -5876,19 +5884,19 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D196" s="3">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3">
@@ -5897,19 +5905,19 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D197" s="3">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3">
@@ -5918,19 +5926,19 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D198" s="3">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3">
@@ -5939,19 +5947,19 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D199" s="3">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3">
@@ -5960,19 +5968,19 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D200" s="3">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3">
@@ -5981,19 +5989,19 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D201" s="3">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3">
@@ -6002,19 +6010,19 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D202" s="3">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3">
@@ -6023,19 +6031,19 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D203" s="3">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3">
@@ -6044,19 +6052,19 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D204" s="3">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3">
@@ -6065,19 +6073,19 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D205" s="3">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3">
@@ -6086,19 +6094,19 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D206" s="3">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3">
@@ -6107,19 +6115,19 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D207" s="3">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3">
@@ -6128,19 +6136,19 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D208" s="3">
-        <v>135</v>
+        <v>44</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3">
@@ -6149,19 +6157,19 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D209" s="3">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3">
@@ -6170,19 +6178,19 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D210" s="3">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3">
@@ -6191,19 +6199,19 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D211" s="3">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3">
@@ -6212,19 +6220,19 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D212" s="3">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3">
@@ -6233,19 +6241,19 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D213" s="3">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3">
@@ -6254,19 +6262,19 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D214" s="3">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3">
@@ -6275,19 +6283,19 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D215" s="3">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3">
@@ -6296,19 +6304,19 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D216" s="3">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3">
@@ -6317,19 +6325,19 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D217" s="3">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3">
@@ -6338,19 +6346,19 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D218" s="3">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3">
@@ -6359,19 +6367,19 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D219" s="3">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3">
@@ -6380,19 +6388,19 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D220" s="3">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3">
@@ -6401,19 +6409,19 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D221" s="3">
-        <v>148</v>
+        <v>42</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3">
@@ -6422,19 +6430,19 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D222" s="3">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3">
@@ -6443,19 +6451,19 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D223" s="3">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3">
@@ -6464,19 +6472,19 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D224" s="3">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3">
@@ -6485,19 +6493,19 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D225" s="3">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3">
@@ -6506,19 +6514,19 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D226" s="3">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3">
@@ -6527,19 +6535,19 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D227" s="3">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3">
@@ -6548,19 +6556,19 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D228" s="3">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3">
@@ -6569,19 +6577,19 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D229" s="3">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3">
@@ -6590,19 +6598,19 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D230" s="3">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3">
@@ -6611,19 +6619,19 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D231" s="3">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3">
@@ -6632,19 +6640,19 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D232" s="3">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3">
@@ -6653,19 +6661,19 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D233" s="3">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3">
@@ -6674,19 +6682,19 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D234" s="3">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3">
@@ -6695,19 +6703,19 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D235" s="3">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3">
@@ -6716,19 +6724,19 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D236" s="3">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3">
@@ -6737,19 +6745,19 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D237" s="3">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3">
@@ -6758,19 +6766,19 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D238" s="3">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3">
@@ -6779,19 +6787,19 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D239" s="3">
-        <v>166</v>
+        <v>52</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3">
@@ -6800,19 +6808,19 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D240" s="3">
-        <v>167</v>
+        <v>52</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3">
@@ -6821,19 +6829,19 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D241" s="3">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3">
@@ -6842,19 +6850,19 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D242" s="3">
-        <v>169</v>
+        <v>53</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3">
@@ -6863,19 +6871,19 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D243" s="3">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3">
@@ -6884,19 +6892,19 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D244" s="3">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3">
@@ -6905,19 +6913,19 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D245" s="3">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3">
@@ -6926,19 +6934,19 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D246" s="3">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3">
@@ -6947,19 +6955,19 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D247" s="3">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3">
@@ -6968,19 +6976,19 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D248" s="3">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3">
@@ -6989,19 +6997,19 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D249" s="3">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3">
@@ -7010,19 +7018,19 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D250" s="3">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3">
@@ -7031,19 +7039,19 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D251" s="3">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3">
@@ -7052,19 +7060,19 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D252" s="3">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3">
@@ -7073,19 +7081,19 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D253" s="3">
-        <v>180</v>
+        <v>57</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3">
@@ -7094,19 +7102,19 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D254" s="3">
-        <v>181</v>
+        <v>57</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3">
@@ -7115,19 +7123,19 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D255" s="3">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3">
@@ -7136,19 +7144,19 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D256" s="3">
-        <v>183</v>
+        <v>58</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3">
@@ -7157,19 +7165,19 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D257" s="3">
-        <v>184</v>
+        <v>58</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3">
@@ -7178,19 +7186,19 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D258" s="3">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3">
@@ -7199,19 +7207,19 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D259" s="3">
-        <v>186</v>
+        <v>62</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3">
@@ -7220,19 +7228,19 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D260" s="3">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3">
@@ -7241,19 +7249,19 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D261" s="3">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3">
@@ -7262,19 +7270,19 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D262" s="3">
-        <v>189</v>
+        <v>61</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3">
@@ -7283,19 +7291,19 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D263" s="3">
-        <v>190</v>
+        <v>61</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3">
@@ -7304,19 +7312,19 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D264" s="3">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3">
@@ -7325,19 +7333,19 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D265" s="3">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3">
@@ -7346,19 +7354,19 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D266" s="3">
-        <v>193</v>
+        <v>60</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3">
@@ -7367,19 +7375,19 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D267" s="3">
-        <v>194</v>
+        <v>60</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3">
@@ -7388,19 +7396,19 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D268" s="3">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3">
@@ -7409,19 +7417,19 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D269" s="3">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3">
@@ -7430,19 +7438,19 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D270" s="3">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3">
@@ -7451,19 +7459,19 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D271" s="3">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3">
@@ -7472,19 +7480,19 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D272" s="3">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3">
@@ -7493,19 +7501,19 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D273" s="3">
-        <v>200</v>
+        <v>66</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3">
@@ -7514,19 +7522,19 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D274" s="3">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3">
@@ -7535,19 +7543,19 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D275" s="3">
-        <v>202</v>
+        <v>63</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3">
@@ -7556,19 +7564,19 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D276" s="3">
-        <v>203</v>
+        <v>63</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3">
@@ -7577,19 +7585,19 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D277" s="3">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3">
@@ -7598,19 +7606,19 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D278" s="3">
-        <v>205</v>
+        <v>68</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3">
@@ -7619,19 +7627,19 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D279" s="3">
-        <v>206</v>
+        <v>69</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3">
@@ -7640,19 +7648,19 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D280" s="3">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3">
@@ -7661,19 +7669,19 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D281" s="3">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3">
@@ -7682,19 +7690,19 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D282" s="3">
-        <v>209</v>
+        <v>69</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3">
@@ -7703,19 +7711,19 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D283" s="3">
-        <v>210</v>
+        <v>67</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3">
@@ -7724,19 +7732,19 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D284" s="3">
-        <v>211</v>
+        <v>67</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3">
@@ -7745,19 +7753,19 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D285" s="3">
-        <v>212</v>
+        <v>67</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3">
@@ -7766,19 +7774,19 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D286" s="3">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3">
@@ -7787,19 +7795,19 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D287" s="3">
-        <v>214</v>
+        <v>64</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3">
@@ -7808,19 +7816,19 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D288" s="3">
-        <v>215</v>
+        <v>64</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3">
@@ -7829,19 +7837,19 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D289" s="3">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3">
@@ -7850,19 +7858,19 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D290" s="3">
-        <v>217</v>
+        <v>65</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3">
@@ -7871,19 +7879,19 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D291" s="3">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3">
@@ -7892,19 +7900,19 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D292" s="3">
-        <v>219</v>
+        <v>70</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3">
@@ -7913,19 +7921,19 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D293" s="3">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3">
@@ -7934,19 +7942,19 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D294" s="3">
-        <v>221</v>
+        <v>71</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3">
@@ -7955,19 +7963,19 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D295" s="3">
-        <v>222</v>
+        <v>71</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3">
@@ -7976,19 +7984,19 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D296" s="3">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3">
@@ -7997,19 +8005,19 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D297" s="3">
-        <v>224</v>
+        <v>1</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3">
@@ -8018,19 +8026,19 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D298" s="3">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3">
@@ -8039,19 +8047,19 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D299" s="3">
-        <v>226</v>
+        <v>1</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3">
@@ -8060,19 +8068,19 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D300" s="3">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3">
@@ -8081,19 +8089,19 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D301" s="3">
-        <v>228</v>
+        <v>1</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3">
@@ -8102,19 +8110,19 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D302" s="3">
-        <v>229</v>
+        <v>1</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3">
@@ -8123,19 +8131,19 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D303" s="3">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3">
@@ -8144,19 +8152,19 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D304" s="3">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3">
@@ -8165,19 +8173,19 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D305" s="3">
-        <v>232</v>
+        <v>72</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3">
@@ -8186,19 +8194,19 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D306" s="3">
-        <v>233</v>
+        <v>72</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3">
@@ -8207,19 +8215,19 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D307" s="3">
-        <v>234</v>
+        <v>74</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3">
@@ -8228,19 +8236,19 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D308" s="3">
-        <v>235</v>
+        <v>74</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3">
@@ -8249,19 +8257,19 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D309" s="3">
-        <v>236</v>
+        <v>74</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3">
@@ -8270,19 +8278,19 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D310" s="3">
-        <v>237</v>
+        <v>74</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3">
@@ -8291,19 +8299,19 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D311" s="3">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3">
@@ -8312,19 +8320,19 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D312" s="3">
-        <v>239</v>
+        <v>75</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3">
@@ -8333,19 +8341,19 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D313" s="3">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3">
@@ -8354,19 +8362,19 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D314" s="3">
-        <v>241</v>
+        <v>73</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3">
@@ -8375,19 +8383,19 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D315" s="3">
-        <v>242</v>
+        <v>73</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3">
@@ -8396,19 +8404,19 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D316" s="3">
-        <v>243</v>
+        <v>73</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3">
@@ -8417,19 +8425,19 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D317" s="3">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3">
@@ -8438,19 +8446,19 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D318" s="3">
-        <v>245</v>
+        <v>74</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3">
@@ -8459,19 +8467,19 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D319" s="3">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3">
@@ -8480,19 +8488,19 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D320" s="3">
-        <v>247</v>
+        <v>74</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3">

--- a/src/data/images_tombstones.xlsx
+++ b/src/data/images_tombstones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_projects\tombstones\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DC4710-59D9-443C-BBCC-BDC0E3D270D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AECD781-C8A8-4ED9-BAD2-3BD747210EB0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,12 +186,6 @@
     <t>2023_05_03_Srednie_Aty_2_front_ortho_id20.jpg</t>
   </si>
   <si>
-    <t>2023_05_03_Srednyaya_Kladbishe_Serda_front_dem_3.jpg</t>
-  </si>
-  <si>
-    <t>2023_05_03_Srednyaya_Kladbishe_Serda_front_ortho_3.jpg</t>
-  </si>
-  <si>
     <t>2023_05_03_Srednyaya_Serda_Kladbishe_3_left_dem_id24.jpg</t>
   </si>
   <si>
@@ -1015,6 +1009,12 @@
   </si>
   <si>
     <t>2023_05_03_Srednyaya_Serda_Kladbishe_1_front_ortho_id22.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_Kladbishe_3_front_dem_id24.jpg</t>
+  </si>
+  <si>
+    <t>2023_05_03_Srednyaya_Serda_Kladbishe_3_front_ortho_id24.jpg</t>
   </si>
 </sst>
 </file>
@@ -1933,40 +1933,40 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D2" s="4">
         <v>47</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
@@ -1975,17 +1975,17 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D3" s="4">
         <v>14</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
@@ -1994,17 +1994,17 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D4" s="4">
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
@@ -2013,17 +2013,17 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D5" s="4">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D6" s="4">
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
@@ -2051,17 +2051,17 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D7" s="4">
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
@@ -2070,17 +2070,17 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D8" s="4">
         <v>58</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4">
@@ -2089,17 +2089,17 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D9" s="4">
         <v>52</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4">
@@ -2108,17 +2108,17 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D10" s="4">
         <v>53</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
@@ -2127,17 +2127,17 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D11" s="4">
         <v>74</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
@@ -2146,17 +2146,17 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D12" s="4">
         <v>75</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
@@ -2165,17 +2165,17 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D13" s="4">
         <v>21</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
@@ -2184,17 +2184,17 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D14" s="4">
         <v>20</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4">
@@ -2203,17 +2203,17 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D15" s="4">
         <v>17</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
@@ -2222,17 +2222,17 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D16" s="4">
         <v>18</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
@@ -2241,17 +2241,17 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D17" s="4">
         <v>22</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
@@ -2260,17 +2260,17 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D18" s="4">
         <v>23</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
@@ -2279,17 +2279,17 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D19" s="4">
         <v>24</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
@@ -2298,17 +2298,17 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D20" s="4">
         <v>25</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4">
@@ -2317,17 +2317,17 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D21" s="4">
         <v>42</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
@@ -2336,17 +2336,17 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D22" s="4">
         <v>43</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4">
@@ -2355,17 +2355,17 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D23" s="4">
         <v>7</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4">
@@ -2374,17 +2374,17 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D24" s="4">
         <v>8</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
@@ -2393,17 +2393,17 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D25" s="4">
         <v>9</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4">
@@ -2412,17 +2412,17 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D26" s="4">
         <v>63</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4">
@@ -2431,17 +2431,17 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
@@ -2450,17 +2450,17 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D28" s="4">
         <v>57</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4">
@@ -2469,17 +2469,17 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D29" s="4">
         <v>62</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4">
@@ -2488,17 +2488,17 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D30" s="4">
         <v>61</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4">
@@ -2507,17 +2507,17 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D31" s="4">
         <v>60</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4">
@@ -2526,17 +2526,17 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D32" s="4">
         <v>11</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4">
@@ -2545,17 +2545,17 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D33" s="4">
         <v>12</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4">
@@ -2564,17 +2564,17 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D34" s="4">
         <v>73</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4">
@@ -2583,17 +2583,17 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D35" s="4">
         <v>54</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4">
@@ -2602,17 +2602,17 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D36" s="4">
         <v>55</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4">
@@ -2621,17 +2621,17 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D37" s="4">
         <v>71</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4">
@@ -2640,17 +2640,17 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D38" s="4">
         <v>68</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4">
@@ -2659,17 +2659,17 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D39" s="4">
         <v>69</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4">
@@ -2678,17 +2678,17 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D40" s="4">
         <v>67</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4">
@@ -2697,17 +2697,17 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D41" s="4">
         <v>59</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4">
@@ -2716,17 +2716,17 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D42" s="4">
         <v>19</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4">
@@ -2735,17 +2735,17 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D43" s="4">
         <v>64</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4">
@@ -2754,17 +2754,17 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D44" s="4">
         <v>65</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4">
@@ -2773,17 +2773,17 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D45" s="4">
         <v>28</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4">
@@ -2792,17 +2792,17 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D46" s="4">
         <v>30</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4">
@@ -2811,17 +2811,17 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D47" s="4">
         <v>31</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4">
@@ -2830,17 +2830,17 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D48" s="4">
         <v>33</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4">
@@ -2849,17 +2849,17 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D49" s="4">
         <v>32</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4">
@@ -2868,17 +2868,17 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D50" s="4">
         <v>29</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4">
@@ -2887,17 +2887,17 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D51" s="4">
         <v>40</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4">
@@ -2906,17 +2906,17 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D52" s="4">
         <v>49</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4">
@@ -2925,17 +2925,17 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D53" s="4">
         <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4">
@@ -2944,17 +2944,17 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D54" s="4">
         <v>72</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4">
@@ -2963,17 +2963,17 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D55" s="4">
         <v>66</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4">
@@ -2982,17 +2982,17 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D56" s="4">
         <v>70</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4">
@@ -3001,17 +3001,17 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D57" s="4">
         <v>48</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4">
@@ -3020,17 +3020,17 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D58" s="4">
         <v>36</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4">
@@ -3039,17 +3039,17 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D59" s="4">
         <v>38</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4">
@@ -3058,17 +3058,17 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D60" s="4">
         <v>37</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4">
@@ -3077,17 +3077,17 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D61" s="4">
         <v>39</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4">
@@ -3096,17 +3096,17 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D62" s="4">
         <v>50</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4">
@@ -3115,17 +3115,17 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D63" s="4">
         <v>51</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4">
@@ -3134,17 +3134,17 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D64" s="4">
         <v>10</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4">
@@ -3153,17 +3153,17 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D65" s="4">
         <v>41</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4">
@@ -3172,17 +3172,17 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D66" s="4">
         <v>26</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4">
@@ -3191,17 +3191,17 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D67" s="4">
         <v>27</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="4">
@@ -3210,17 +3210,17 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D68" s="4">
         <v>34</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4">
@@ -3229,17 +3229,17 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D69" s="4">
         <v>1</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4">
@@ -3248,17 +3248,17 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D70" s="4">
         <v>35</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4">
@@ -3267,17 +3267,17 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D71" s="4">
         <v>35</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4">
@@ -3286,17 +3286,17 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D72" s="4">
         <v>44</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4">
@@ -3305,17 +3305,17 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D73" s="4">
         <v>45</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4">
@@ -3324,17 +3324,17 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D74" s="4">
         <v>46</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4">
@@ -3343,13 +3343,13 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -3364,13 +3364,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D76" s="3">
         <v>2</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D77" s="3">
         <v>4</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D78" s="3">
         <v>4</v>
@@ -3427,13 +3427,13 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D79" s="3">
         <v>5</v>
@@ -3448,13 +3448,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D80" s="3">
         <v>5</v>
@@ -3469,13 +3469,13 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D81" s="3">
         <v>5</v>
@@ -3490,13 +3490,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D82" s="3">
         <v>5</v>
@@ -3511,13 +3511,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D83" s="3">
         <v>6</v>
@@ -3532,13 +3532,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D84" s="3">
         <v>6</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D85" s="3">
         <v>6</v>
@@ -3574,13 +3574,13 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D86" s="3">
         <v>6</v>
@@ -3595,13 +3595,13 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D87" s="3">
         <v>3</v>
@@ -3616,13 +3616,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D88" s="3">
         <v>3</v>
@@ -3637,13 +3637,13 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D89" s="3">
         <v>3</v>
@@ -3658,13 +3658,13 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D90" s="3">
         <v>3</v>
@@ -3679,13 +3679,13 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D91" s="3">
         <v>16</v>
@@ -3700,13 +3700,13 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D92" s="3">
         <v>16</v>
@@ -3721,13 +3721,13 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D93" s="3">
         <v>16</v>
@@ -3742,13 +3742,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D94" s="3">
         <v>16</v>
@@ -3763,13 +3763,13 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D95" s="3">
         <v>10</v>
@@ -3784,13 +3784,13 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D96" s="3">
         <v>10</v>
@@ -3805,13 +3805,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D97" s="3">
         <v>15</v>
@@ -3826,13 +3826,13 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D98" s="3">
         <v>15</v>
@@ -3847,13 +3847,13 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D99" s="3">
         <v>14</v>
@@ -3868,13 +3868,13 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D100" s="3">
         <v>14</v>
@@ -3889,13 +3889,13 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D101" s="3">
         <v>13</v>
@@ -3910,13 +3910,13 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D102" s="3">
         <v>13</v>
@@ -3931,13 +3931,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D103" s="3">
         <v>7</v>
@@ -3952,13 +3952,13 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D104" s="3">
         <v>7</v>
@@ -3973,13 +3973,13 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D105" s="3">
         <v>8</v>
@@ -3994,13 +3994,13 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D106" s="3">
         <v>8</v>
@@ -4015,13 +4015,13 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D107" s="3">
         <v>9</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D108" s="3">
         <v>9</v>
@@ -4057,13 +4057,13 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D109" s="3">
         <v>9</v>
@@ -4078,13 +4078,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D110" s="3">
         <v>9</v>
@@ -4099,13 +4099,13 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D111" s="3">
         <v>0</v>
@@ -4120,13 +4120,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D112" s="3">
         <v>0</v>
@@ -4141,13 +4141,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D113" s="3">
         <v>0</v>
@@ -4162,13 +4162,13 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D114" s="3">
         <v>0</v>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D115" s="3">
         <v>11</v>
@@ -4204,13 +4204,13 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D116" s="3">
         <v>11</v>
@@ -4225,13 +4225,13 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D117" s="3">
         <v>12</v>
@@ -4246,13 +4246,13 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D118" s="3">
         <v>12</v>
@@ -4267,13 +4267,13 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D119" s="3">
         <v>12</v>
@@ -4288,13 +4288,13 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D120" s="3">
         <v>12</v>
@@ -4309,13 +4309,13 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D121" s="3">
         <v>21</v>
@@ -4330,13 +4330,13 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D122" s="3">
         <v>21</v>
@@ -4351,13 +4351,13 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D123" s="3">
         <v>20</v>
@@ -4372,13 +4372,13 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D124" s="3">
         <v>20</v>
@@ -4393,13 +4393,13 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D125" s="3">
         <v>20</v>
@@ -4414,13 +4414,13 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D126" s="3">
         <v>20</v>
@@ -4435,55 +4435,55 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D127" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>52</v>
+        <v>313</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D128" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>53</v>
+        <v>314</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D129" s="3">
         <v>17</v>
@@ -4493,18 +4493,18 @@
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D130" s="3">
         <v>17</v>
@@ -4514,60 +4514,60 @@
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D131" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>317</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D132" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>318</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D133" s="3">
         <v>18</v>
@@ -4577,18 +4577,18 @@
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D134" s="3">
         <v>18</v>
@@ -4598,60 +4598,60 @@
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D135" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D136" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D137" s="3">
         <v>22</v>
@@ -4661,18 +4661,18 @@
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D138" s="3">
         <v>22</v>
@@ -4682,24 +4682,24 @@
       </c>
       <c r="F138" s="3"/>
       <c r="G138" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D139" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3">
@@ -4708,19 +4708,19 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D140" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="3">
@@ -4729,19 +4729,19 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D141" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3">
@@ -4750,19 +4750,19 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D142" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3">
@@ -4771,19 +4771,19 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D143" s="3">
         <v>24</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3">
@@ -4792,19 +4792,19 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D144" s="3">
         <v>24</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3">
@@ -4813,19 +4813,19 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D145" s="3">
         <v>24</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3">
@@ -4834,19 +4834,19 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D146" s="3">
         <v>24</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3">
@@ -4855,19 +4855,19 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D147" s="3">
         <v>25</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3">
@@ -4876,19 +4876,19 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D148" s="3">
         <v>25</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3">
@@ -4897,19 +4897,19 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D149" s="3">
         <v>19</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3">
@@ -4918,19 +4918,19 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D150" s="3">
         <v>19</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="3">
@@ -4939,19 +4939,19 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D151" s="3">
         <v>19</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3">
@@ -4960,19 +4960,19 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D152" s="3">
         <v>19</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3">
@@ -4981,19 +4981,19 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D153" s="3">
         <v>26</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3">
@@ -5002,19 +5002,19 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D154" s="3">
         <v>26</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3">
@@ -5023,19 +5023,19 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D155" s="3">
         <v>27</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3">
@@ -5044,19 +5044,19 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D156" s="3">
         <v>27</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3">
@@ -5065,19 +5065,19 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D157" s="3">
         <v>40</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3">
@@ -5086,19 +5086,19 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D158" s="3">
         <v>40</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3">
@@ -5107,19 +5107,19 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D159" s="3">
         <v>40</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3">
@@ -5128,19 +5128,19 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D160" s="3">
         <v>40</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3">
@@ -5149,19 +5149,19 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D161" s="3">
         <v>34</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3">
@@ -5170,19 +5170,19 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D162" s="3">
         <v>34</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3">
@@ -5191,19 +5191,19 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D163" s="3">
         <v>34</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3">
@@ -5212,19 +5212,19 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D164" s="3">
         <v>34</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3">
@@ -5233,19 +5233,19 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D165" s="3">
         <v>28</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3">
@@ -5254,19 +5254,19 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D166" s="3">
         <v>28</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3">
@@ -5275,19 +5275,19 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D167" s="3">
         <v>30</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3">
@@ -5296,19 +5296,19 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D168" s="3">
         <v>30</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3">
@@ -5317,19 +5317,19 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D169" s="3">
         <v>31</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3">
@@ -5338,19 +5338,19 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D170" s="3">
         <v>31</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3">
@@ -5359,19 +5359,19 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D171" s="3">
         <v>33</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3">
@@ -5380,19 +5380,19 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D172" s="3">
         <v>33</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3">
@@ -5401,19 +5401,19 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D173" s="3">
         <v>33</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3">
@@ -5422,19 +5422,19 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D174" s="3">
         <v>33</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3">
@@ -5443,19 +5443,19 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D175" s="3">
         <v>32</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3">
@@ -5464,19 +5464,19 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D176" s="3">
         <v>32</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3">
@@ -5485,19 +5485,19 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D177" s="3">
         <v>29</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3">
@@ -5506,19 +5506,19 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D178" s="3">
         <v>29</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3">
@@ -5527,19 +5527,19 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D179" s="3">
         <v>29</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3">
@@ -5548,19 +5548,19 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D180" s="3">
         <v>29</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3">
@@ -5569,19 +5569,19 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D181" s="3">
         <v>36</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3">
@@ -5590,19 +5590,19 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D182" s="3">
         <v>36</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3">
@@ -5611,19 +5611,19 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D183" s="3">
         <v>36</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3">
@@ -5632,19 +5632,19 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D184" s="3">
         <v>36</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3">
@@ -5653,19 +5653,19 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D185" s="3">
         <v>38</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3">
@@ -5674,19 +5674,19 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D186" s="3">
         <v>38</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3">
@@ -5695,19 +5695,19 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D187" s="3">
         <v>37</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3">
@@ -5716,19 +5716,19 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D188" s="3">
         <v>37</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3">
@@ -5737,19 +5737,19 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D189" s="3">
         <v>37</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3">
@@ -5758,19 +5758,19 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D190" s="3">
         <v>37</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3">
@@ -5779,19 +5779,19 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D191" s="3">
         <v>39</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3">
@@ -5800,19 +5800,19 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D192" s="3">
         <v>39</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3">
@@ -5821,19 +5821,19 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D193" s="3">
         <v>39</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3">
@@ -5842,19 +5842,19 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D194" s="3">
         <v>39</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3">
@@ -5863,19 +5863,19 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D195" s="3">
         <v>35</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3">
@@ -5884,19 +5884,19 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D196" s="3">
         <v>35</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3">
@@ -5905,19 +5905,19 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D197" s="3">
         <v>35</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3">
@@ -5926,19 +5926,19 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D198" s="3">
         <v>35</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3">
@@ -5947,19 +5947,19 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D199" s="3">
         <v>35</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3">
@@ -5968,19 +5968,19 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D200" s="3">
         <v>35</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3">
@@ -5989,19 +5989,19 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D201" s="3">
         <v>41</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3">
@@ -6010,19 +6010,19 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D202" s="3">
         <v>41</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3">
@@ -6031,19 +6031,19 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D203" s="3">
         <v>41</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3">
@@ -6052,19 +6052,19 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D204" s="3">
         <v>41</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3">
@@ -6073,19 +6073,19 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D205" s="3">
         <v>44</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3">
@@ -6094,19 +6094,19 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D206" s="3">
         <v>44</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3">
@@ -6115,19 +6115,19 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D207" s="3">
         <v>44</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3">
@@ -6136,19 +6136,19 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D208" s="3">
         <v>44</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3">
@@ -6157,19 +6157,19 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D209" s="3">
         <v>45</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3">
@@ -6178,19 +6178,19 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D210" s="3">
         <v>45</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3">
@@ -6199,19 +6199,19 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D211" s="3">
         <v>45</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3">
@@ -6220,19 +6220,19 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D212" s="3">
         <v>45</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3">
@@ -6241,19 +6241,19 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D213" s="3">
         <v>46</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3">
@@ -6262,19 +6262,19 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D214" s="3">
         <v>46</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3">
@@ -6283,19 +6283,19 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D215" s="3">
         <v>46</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3">
@@ -6304,19 +6304,19 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D216" s="3">
         <v>46</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3">
@@ -6325,19 +6325,19 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D217" s="3">
         <v>47</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3">
@@ -6346,19 +6346,19 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D218" s="3">
         <v>47</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3">
@@ -6367,19 +6367,19 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D219" s="3">
         <v>47</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3">
@@ -6388,19 +6388,19 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D220" s="3">
         <v>47</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3">
@@ -6409,19 +6409,19 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D221" s="3">
         <v>42</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3">
@@ -6430,19 +6430,19 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D222" s="3">
         <v>42</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3">
@@ -6451,19 +6451,19 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D223" s="3">
         <v>43</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3">
@@ -6472,19 +6472,19 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D224" s="3">
         <v>43</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3">
@@ -6493,19 +6493,19 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D225" s="3">
         <v>49</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3">
@@ -6514,19 +6514,19 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D226" s="3">
         <v>49</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3">
@@ -6535,19 +6535,19 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D227" s="3">
         <v>49</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3">
@@ -6556,19 +6556,19 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D228" s="3">
         <v>49</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3">
@@ -6577,19 +6577,19 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D229" s="3">
         <v>48</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3">
@@ -6598,19 +6598,19 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D230" s="3">
         <v>48</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3">
@@ -6619,19 +6619,19 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D231" s="3">
         <v>48</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3">
@@ -6640,19 +6640,19 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D232" s="3">
         <v>48</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3">
@@ -6661,19 +6661,19 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D233" s="3">
         <v>50</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3">
@@ -6682,19 +6682,19 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D234" s="3">
         <v>50</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3">
@@ -6703,19 +6703,19 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D235" s="3">
         <v>51</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3">
@@ -6724,19 +6724,19 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D236" s="3">
         <v>51</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3">
@@ -6745,19 +6745,19 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D237" s="3">
         <v>52</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3">
@@ -6766,19 +6766,19 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D238" s="3">
         <v>52</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3">
@@ -6787,19 +6787,19 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D239" s="3">
         <v>52</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3">
@@ -6808,19 +6808,19 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D240" s="3">
         <v>52</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3">
@@ -6829,19 +6829,19 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D241" s="3">
         <v>53</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3">
@@ -6850,19 +6850,19 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D242" s="3">
         <v>53</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3">
@@ -6871,19 +6871,19 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D243" s="3">
         <v>54</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3">
@@ -6892,19 +6892,19 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D244" s="3">
         <v>54</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3">
@@ -6913,19 +6913,19 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D245" s="3">
         <v>55</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3">
@@ -6934,19 +6934,19 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D246" s="3">
         <v>55</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3">
@@ -6955,19 +6955,19 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D247" s="3">
         <v>55</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3">
@@ -6976,19 +6976,19 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D248" s="3">
         <v>55</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3">
@@ -6997,19 +6997,19 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D249" s="3">
         <v>56</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3">
@@ -7018,19 +7018,19 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D250" s="3">
         <v>56</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3">
@@ -7039,19 +7039,19 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D251" s="3">
         <v>57</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3">
@@ -7060,19 +7060,19 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D252" s="3">
         <v>57</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3">
@@ -7081,19 +7081,19 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D253" s="3">
         <v>57</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3">
@@ -7102,19 +7102,19 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D254" s="3">
         <v>57</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3">
@@ -7123,19 +7123,19 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D255" s="3">
         <v>58</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3">
@@ -7144,19 +7144,19 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D256" s="3">
         <v>58</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3">
@@ -7165,19 +7165,19 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D257" s="3">
         <v>58</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3">
@@ -7186,19 +7186,19 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D258" s="3">
         <v>58</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3">
@@ -7207,19 +7207,19 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D259" s="3">
         <v>62</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3">
@@ -7228,19 +7228,19 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D260" s="3">
         <v>62</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3">
@@ -7249,19 +7249,19 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D261" s="3">
         <v>61</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3">
@@ -7270,19 +7270,19 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D262" s="3">
         <v>61</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3">
@@ -7291,19 +7291,19 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D263" s="3">
         <v>61</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3">
@@ -7312,19 +7312,19 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D264" s="3">
         <v>61</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3">
@@ -7333,19 +7333,19 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D265" s="3">
         <v>60</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3">
@@ -7354,19 +7354,19 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D266" s="3">
         <v>60</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3">
@@ -7375,19 +7375,19 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D267" s="3">
         <v>60</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3">
@@ -7396,19 +7396,19 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D268" s="3">
         <v>60</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3">
@@ -7417,19 +7417,19 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D269" s="3">
         <v>59</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3">
@@ -7438,19 +7438,19 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D270" s="3">
         <v>59</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3">
@@ -7459,19 +7459,19 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D271" s="3">
         <v>66</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3">
@@ -7480,19 +7480,19 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D272" s="3">
         <v>66</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3">
@@ -7501,19 +7501,19 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D273" s="3">
         <v>66</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3">
@@ -7522,19 +7522,19 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D274" s="3">
         <v>66</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3">
@@ -7543,19 +7543,19 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D275" s="3">
         <v>63</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3">
@@ -7564,19 +7564,19 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D276" s="3">
         <v>63</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3">
@@ -7585,19 +7585,19 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D277" s="3">
         <v>68</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3">
@@ -7606,19 +7606,19 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D278" s="3">
         <v>68</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3">
@@ -7627,19 +7627,19 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D279" s="3">
         <v>69</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3">
@@ -7648,19 +7648,19 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D280" s="3">
         <v>69</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3">
@@ -7669,19 +7669,19 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D281" s="3">
         <v>69</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3">
@@ -7690,19 +7690,19 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D282" s="3">
         <v>69</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3">
@@ -7711,19 +7711,19 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D283" s="3">
         <v>67</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3">
@@ -7732,19 +7732,19 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D284" s="3">
         <v>67</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3">
@@ -7753,19 +7753,19 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D285" s="3">
         <v>67</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3">
@@ -7774,19 +7774,19 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D286" s="3">
         <v>67</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3">
@@ -7795,19 +7795,19 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D287" s="3">
         <v>64</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3">
@@ -7816,19 +7816,19 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D288" s="3">
         <v>64</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3">
@@ -7837,19 +7837,19 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D289" s="3">
         <v>65</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3">
@@ -7858,19 +7858,19 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D290" s="3">
         <v>65</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3">
@@ -7879,19 +7879,19 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D291" s="3">
         <v>70</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3">
@@ -7900,19 +7900,19 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D292" s="3">
         <v>70</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3">
@@ -7921,19 +7921,19 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D293" s="3">
         <v>71</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3">
@@ -7942,19 +7942,19 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D294" s="3">
         <v>71</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3">
@@ -7963,19 +7963,19 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D295" s="3">
         <v>71</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3">
@@ -7984,19 +7984,19 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D296" s="3">
         <v>71</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3">
@@ -8005,19 +8005,19 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D297" s="3">
         <v>1</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3">
@@ -8026,19 +8026,19 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D298" s="3">
         <v>1</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3">
@@ -8047,19 +8047,19 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D299" s="3">
         <v>1</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3">
@@ -8068,19 +8068,19 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D300" s="3">
         <v>1</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3">
@@ -8089,19 +8089,19 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D301" s="3">
         <v>1</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3">
@@ -8110,19 +8110,19 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D302" s="3">
         <v>1</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3">
@@ -8131,19 +8131,19 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D303" s="3">
         <v>72</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3">
@@ -8152,19 +8152,19 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D304" s="3">
         <v>72</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3">
@@ -8173,19 +8173,19 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D305" s="3">
         <v>72</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3">
@@ -8194,19 +8194,19 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D306" s="3">
         <v>72</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3">
@@ -8215,19 +8215,19 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D307" s="3">
         <v>74</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3">
@@ -8236,19 +8236,19 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D308" s="3">
         <v>74</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3">
@@ -8257,19 +8257,19 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D309" s="3">
         <v>74</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3">
@@ -8278,19 +8278,19 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D310" s="3">
         <v>74</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3">
@@ -8299,19 +8299,19 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D311" s="3">
         <v>75</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3">
@@ -8320,19 +8320,19 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D312" s="3">
         <v>75</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3">
@@ -8341,19 +8341,19 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D313" s="3">
         <v>73</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3">
@@ -8362,19 +8362,19 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D314" s="3">
         <v>73</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3">
@@ -8383,19 +8383,19 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D315" s="3">
         <v>73</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3">
@@ -8404,19 +8404,19 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D316" s="3">
         <v>73</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3">
@@ -8425,19 +8425,19 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D317" s="3">
         <v>74</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3">
@@ -8446,19 +8446,19 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D318" s="3">
         <v>74</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3">
@@ -8467,19 +8467,19 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D319" s="3">
         <v>74</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3">
@@ -8488,19 +8488,19 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D320" s="3">
         <v>74</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3">
